--- a/12624002.xlsx
+++ b/12624002.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PIYUSH PARMAR\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c135914e813e79f/Desktop/python/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{399E9875-3776-4171-B3BA-4E85D398279E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -223,6 +223,9 @@
   </si>
   <si>
     <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -503,10 +506,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1304,81 +1303,147 @@
         <f t="shared" si="1"/>
         <v>195</v>
       </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+      <c r="K12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
         <v>46259</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="B13" s="14">
+        <v>500</v>
+      </c>
+      <c r="C13" s="14">
+        <v>90</v>
+      </c>
+      <c r="D13" s="14">
+        <v>50</v>
+      </c>
+      <c r="E13" s="14">
+        <v>0</v>
+      </c>
+      <c r="F13" s="14">
+        <v>350</v>
+      </c>
+      <c r="G13" s="14">
+        <v>7</v>
+      </c>
+      <c r="H13" s="14">
+        <v>250</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
+        <v>200</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
         <v>46260</v>
       </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="B14" s="14">
+        <v>560</v>
+      </c>
+      <c r="C14" s="14">
+        <v>100</v>
+      </c>
+      <c r="D14" s="14">
+        <v>0</v>
+      </c>
+      <c r="E14" s="14">
+        <v>60</v>
+      </c>
+      <c r="F14" s="14">
+        <v>350</v>
+      </c>
+      <c r="G14" s="14">
+        <v>7</v>
+      </c>
+      <c r="H14" s="14">
+        <v>200</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
+        <v>170</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
         <v>46261</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="B15" s="14">
+        <v>600</v>
+      </c>
+      <c r="C15" s="14">
+        <v>100</v>
+      </c>
+      <c r="D15" s="14">
+        <v>70</v>
+      </c>
+      <c r="E15" s="14">
+        <v>50</v>
+      </c>
+      <c r="F15" s="14">
+        <v>200</v>
+      </c>
+      <c r="G15" s="14">
+        <v>4</v>
+      </c>
+      <c r="H15" s="14">
+        <v>300</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
+        <v>120</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">

--- a/12624002.xlsx
+++ b/12624002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c135914e813e79f/Desktop/python/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{399E9875-3776-4171-B3BA-4E85D398279E}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86A27EB7-EC84-4735-8D80-267398E0DB6C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -506,6 +506,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1450,72 +1454,132 @@
       <c r="A16" s="13">
         <v>46262</v>
       </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="B16" s="14">
+        <v>500</v>
+      </c>
+      <c r="C16" s="14">
+        <v>70</v>
+      </c>
+      <c r="D16" s="14">
+        <v>55</v>
+      </c>
+      <c r="E16" s="14">
+        <v>0</v>
+      </c>
+      <c r="F16" s="14">
+        <v>250</v>
+      </c>
+      <c r="G16" s="14">
+        <v>5</v>
+      </c>
+      <c r="H16" s="14">
+        <v>200</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1075</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
+        <v>365</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
         <v>46263</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="B17" s="14">
+        <v>660</v>
+      </c>
+      <c r="C17" s="14">
+        <v>90</v>
+      </c>
+      <c r="D17" s="14">
+        <v>0</v>
+      </c>
+      <c r="E17" s="14">
+        <v>0</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>600</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
+        <v>90</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
         <v>46264</v>
       </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="B18" s="14">
+        <v>630</v>
+      </c>
+      <c r="C18" s="14">
+        <v>0</v>
+      </c>
+      <c r="D18" s="14">
+        <v>80</v>
+      </c>
+      <c r="E18" s="14">
+        <v>60</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>400</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
+        <v>270</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">

--- a/12624002.xlsx
+++ b/12624002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c135914e813e79f/Desktop/python/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86A27EB7-EC84-4735-8D80-267398E0DB6C}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8CF465D-EC31-44C1-8AA2-32A4CA3ADEFD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -226,6 +226,12 @@
   </si>
   <si>
     <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -1583,29 +1589,53 @@
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B19" s="14">
+        <v>520</v>
+      </c>
+      <c r="C19" s="14">
+        <v>100</v>
+      </c>
+      <c r="D19" s="14">
+        <v>70</v>
+      </c>
+      <c r="E19" s="14">
+        <v>50</v>
+      </c>
+      <c r="F19" s="14">
+        <v>250</v>
+      </c>
+      <c r="G19" s="14">
+        <v>5</v>
+      </c>
+      <c r="H19" s="14">
+        <v>400</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
+        <v>50</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
+      <c r="A20" s="13">
+        <v>46266</v>
+      </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>

--- a/12624002.xlsx
+++ b/12624002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c135914e813e79f/Desktop/python/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8CF465D-EC31-44C1-8AA2-32A4CA3ADEFD}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8437570D-DCC9-49B6-975D-1E744E0657F7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1636,28 +1636,50 @@
       <c r="A20" s="13">
         <v>46266</v>
       </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="B20" s="14">
+        <v>530</v>
+      </c>
+      <c r="C20" s="14">
+        <v>90</v>
+      </c>
+      <c r="D20" s="14">
+        <v>55</v>
+      </c>
+      <c r="E20" s="14">
+        <v>40</v>
+      </c>
+      <c r="F20" s="14">
+        <v>350</v>
+      </c>
+      <c r="G20" s="14">
+        <v>7</v>
+      </c>
+      <c r="H20" s="14">
+        <v>350</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1415</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
+        <v>25</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
+      <c r="A21" s="13">
+        <v>46267</v>
+      </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
       <c r="D21" s="14"/>
